--- a/word-lists/100-wordlist-Swedish.xlsx
+++ b/word-lists/100-wordlist-Swedish.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Claude word list docs and files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\KDrive\Project\Keyboard\keyboard heaven - in work\KeyDual Github readme\Wordlist 2026-04-20 files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AFC92DE-BCE0-445E-BAA0-206B2E83509B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE2618CD-B163-4137-BA22-F72EE71B3BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{8D7C7BF7-5DF8-4EE8-B0E9-44AD201E4EDD}"/>
+    <workbookView xWindow="5649" yWindow="2049" windowWidth="24685" windowHeight="13054" xr2:uid="{AAE376C1-1B07-4EC2-8604-8B3FA57768C6}"/>
   </bookViews>
   <sheets>
     <sheet name="100-wordlist-Swedish" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
     <t>punkt</t>
   </si>
   <si>
-    <t>mycke</t>
+    <t>mycket</t>
   </si>
   <si>
     <t>mot</t>
@@ -321,7 +321,7 @@
     <t>arbeta</t>
   </si>
   <si>
-    <t>frågor</t>
+    <t>situation</t>
   </si>
   <si>
     <t>information</t>
@@ -330,7 +330,7 @@
     <t>regering</t>
   </si>
   <si>
-    <t>viktig</t>
+    <t>naturligtvis</t>
   </si>
   <si>
     <t>skillnad</t>
@@ -1193,7 +1193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE146DED-CD77-4835-BEFA-8493DBACF278}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FD721BA-D4D6-42BF-B541-39E9F7E63B96}">
   <dimension ref="A1:C101"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -2217,7 +2217,7 @@
         <v>94</v>
       </c>
       <c r="C93">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.4">
